--- a/utils/monday_sprint_sprint_2025-21.xlsx
+++ b/utils/monday_sprint_sprint_2025-21.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="378">
   <si>
     <t>Ticket</t>
   </si>
@@ -144,6 +144,9 @@
     <t>31/01/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
@@ -180,7 +183,7 @@
     <t>29/09/2025</t>
   </si>
   <si>
-    <t>27/04/2026</t>
+    <t>22/04/2026</t>
   </si>
   <si>
     <t>Setembro</t>
@@ -675,7 +678,7 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>32723</t>
@@ -921,7 +924,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -1026,7 +1029,7 @@
     <t>09/09/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Criar Tipo custo item</t>
@@ -1960,16 +1963,16 @@
         <v>42</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1986,10 +1989,10 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
@@ -2018,7 +2021,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -2030,10 +2033,10 @@
         <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>24</v>
@@ -2062,7 +2065,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -2074,39 +2077,39 @@
         <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -2118,10 +2121,10 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>24</v>
@@ -2150,7 +2153,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -2162,10 +2165,10 @@
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>24</v>
@@ -2183,7 +2186,7 @@
         <v>17</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>27</v>
@@ -2206,10 +2209,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -2238,7 +2241,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -2250,10 +2253,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -2282,7 +2285,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -2294,10 +2297,10 @@
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
@@ -2326,7 +2329,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -2338,10 +2341,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
@@ -2359,7 +2362,7 @@
         <v>17</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>21</v>
@@ -2370,7 +2373,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2382,10 +2385,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -2414,7 +2417,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2426,10 +2429,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>24</v>
@@ -2458,7 +2461,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2470,10 +2473,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>24</v>
@@ -2494,7 +2497,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>17</v>
@@ -2502,7 +2505,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2514,10 +2517,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>24</v>
@@ -2535,7 +2538,7 @@
         <v>17</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>27</v>
@@ -2546,7 +2549,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2558,10 +2561,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>24</v>
@@ -2582,7 +2585,7 @@
         <v>20</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>17</v>
@@ -2590,7 +2593,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2602,10 +2605,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>24</v>
@@ -2634,7 +2637,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2646,10 +2649,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>24</v>
@@ -2670,7 +2673,7 @@
         <v>20</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>17</v>
@@ -2690,10 +2693,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2734,10 +2737,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>24</v>
@@ -2755,7 +2758,7 @@
         <v>17</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>21</v>
@@ -2766,7 +2769,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2778,10 +2781,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>24</v>
@@ -2799,7 +2802,7 @@
         <v>17</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>21</v>
@@ -2822,10 +2825,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2854,7 +2857,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2866,10 +2869,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>24</v>
@@ -2890,7 +2893,7 @@
         <v>20</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>17</v>
@@ -2898,7 +2901,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2910,10 +2913,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2931,7 +2934,7 @@
         <v>17</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>21</v>
@@ -2942,7 +2945,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2954,10 +2957,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>24</v>
@@ -2986,7 +2989,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2998,10 +3001,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>24</v>
@@ -3019,7 +3022,7 @@
         <v>17</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>21</v>
@@ -3030,7 +3033,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -3042,10 +3045,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>24</v>
@@ -3063,7 +3066,7 @@
         <v>17</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>21</v>
@@ -3074,7 +3077,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -3086,10 +3089,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>24</v>
@@ -3107,10 +3110,10 @@
         <v>17</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>17</v>
@@ -3118,7 +3121,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3130,10 +3133,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>24</v>
@@ -3162,7 +3165,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3174,10 +3177,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>24</v>
@@ -3218,10 +3221,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -3250,7 +3253,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3262,10 +3265,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>24</v>
@@ -3283,7 +3286,7 @@
         <v>17</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>27</v>
@@ -3294,7 +3297,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3306,10 +3309,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>24</v>
@@ -3330,7 +3333,7 @@
         <v>20</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>17</v>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3350,10 +3353,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>24</v>
@@ -3382,7 +3385,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3394,10 +3397,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3438,10 +3441,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>24</v>
@@ -3459,7 +3462,7 @@
         <v>17</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>27</v>
@@ -3470,7 +3473,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3482,10 +3485,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>24</v>
@@ -3514,7 +3517,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3526,7 +3529,7 @@
         <v>37</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>17</v>
@@ -3535,30 +3538,30 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3570,10 +3573,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>24</v>
@@ -3602,7 +3605,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3614,10 +3617,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>24</v>
@@ -3646,7 +3649,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3658,10 +3661,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>24</v>
@@ -3690,7 +3693,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3702,10 +3705,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>24</v>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3746,25 +3749,25 @@
         <v>37</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>20</v>
@@ -3773,27 +3776,27 @@
         <v>21</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3822,7 +3825,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3834,10 +3837,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>24</v>
@@ -3858,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>17</v>
@@ -3866,7 +3869,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3878,10 +3881,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>24</v>
@@ -3899,7 +3902,7 @@
         <v>17</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>21</v>
@@ -3910,7 +3913,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3922,10 +3925,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>24</v>
@@ -3946,7 +3949,7 @@
         <v>20</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>17</v>
@@ -3954,7 +3957,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3966,10 +3969,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>24</v>
@@ -3987,7 +3990,7 @@
         <v>17</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>21</v>
@@ -3998,7 +4001,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -4010,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>24</v>
@@ -4042,7 +4045,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -4054,10 +4057,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>24</v>
@@ -4075,7 +4078,7 @@
         <v>17</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>27</v>
@@ -4086,7 +4089,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -4098,10 +4101,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>24</v>
@@ -4130,7 +4133,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -4142,10 +4145,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>24</v>
@@ -4166,7 +4169,7 @@
         <v>20</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>17</v>
@@ -4174,7 +4177,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4186,10 +4189,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>24</v>
@@ -4207,10 +4210,10 @@
         <v>17</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>17</v>
@@ -4218,7 +4221,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4230,10 +4233,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>24</v>
@@ -4262,7 +4265,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4274,10 +4277,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>24</v>
@@ -4295,7 +4298,7 @@
         <v>17</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>21</v>
@@ -4306,7 +4309,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4318,10 +4321,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>24</v>
@@ -4339,7 +4342,7 @@
         <v>17</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>21</v>
@@ -4350,7 +4353,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4362,10 +4365,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4394,7 +4397,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4406,10 +4409,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>24</v>
@@ -4427,7 +4430,7 @@
         <v>17</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>27</v>
@@ -4450,7 +4453,7 @@
         <v>37</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>39</v>
@@ -4468,21 +4471,21 @@
         <v>42</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4494,10 +4497,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>24</v>
@@ -4526,7 +4529,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4538,10 +4541,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>24</v>
@@ -4570,7 +4573,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4582,10 +4585,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>24</v>
@@ -4614,7 +4617,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4626,10 +4629,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>24</v>
@@ -4647,7 +4650,7 @@
         <v>17</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>27</v>
@@ -4658,7 +4661,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4670,10 +4673,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>24</v>
@@ -4702,7 +4705,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4714,10 +4717,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>24</v>
@@ -4735,7 +4738,7 @@
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>27</v>
@@ -4746,22 +4749,22 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>24</v>
@@ -4790,7 +4793,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4802,10 +4805,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>24</v>
@@ -4826,7 +4829,7 @@
         <v>20</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>17</v>
@@ -4834,7 +4837,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4846,10 +4849,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>24</v>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4890,10 +4893,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4911,7 +4914,7 @@
         <v>17</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>21</v>
@@ -4922,7 +4925,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4934,10 +4937,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>24</v>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4978,10 +4981,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4999,7 +5002,7 @@
         <v>17</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>21</v>
@@ -5022,10 +5025,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -5054,7 +5057,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -5066,10 +5069,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>24</v>
@@ -5087,7 +5090,7 @@
         <v>17</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>21</v>
@@ -5098,7 +5101,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5110,10 +5113,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>24</v>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5154,10 +5157,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -5186,7 +5189,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -5198,10 +5201,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -5222,7 +5225,7 @@
         <v>20</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>17</v>
@@ -5230,7 +5233,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5242,39 +5245,39 @@
         <v>37</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5286,10 +5289,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>24</v>
@@ -5318,7 +5321,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5330,10 +5333,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>24</v>
@@ -5351,7 +5354,7 @@
         <v>17</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>21</v>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5374,10 +5377,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>24</v>
@@ -5406,7 +5409,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5418,10 +5421,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>24</v>
@@ -5442,7 +5445,7 @@
         <v>20</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>17</v>
@@ -5450,7 +5453,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5462,10 +5465,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>24</v>
@@ -5486,7 +5489,7 @@
         <v>20</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>17</v>
@@ -5494,7 +5497,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5506,10 +5509,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>24</v>
@@ -5538,7 +5541,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5550,10 +5553,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>24</v>
@@ -5582,7 +5585,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5594,39 +5597,39 @@
         <v>37</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5638,10 +5641,10 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>24</v>
@@ -5670,7 +5673,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5682,10 +5685,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>24</v>
@@ -5703,7 +5706,7 @@
         <v>17</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>27</v>
@@ -5714,7 +5717,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5726,39 +5729,39 @@
         <v>37</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5770,10 +5773,10 @@
         <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>19</v>
@@ -5802,7 +5805,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5814,7 +5817,7 @@
         <v>37</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>17</v>
@@ -5823,30 +5826,30 @@
         <v>19</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5858,10 +5861,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>24</v>
@@ -5890,7 +5893,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5902,10 +5905,10 @@
         <v>17</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>24</v>
@@ -5923,7 +5926,7 @@
         <v>17</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>21</v>
@@ -5934,7 +5937,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5946,10 +5949,10 @@
         <v>17</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>19</v>
@@ -5967,7 +5970,7 @@
         <v>17</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>21</v>
@@ -5978,7 +5981,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -5990,10 +5993,10 @@
         <v>17</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>24</v>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -6034,10 +6037,10 @@
         <v>17</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>19</v>
@@ -6066,22 +6069,22 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>19</v>
@@ -6110,7 +6113,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -6122,10 +6125,10 @@
         <v>17</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>24</v>
@@ -6154,7 +6157,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -6166,10 +6169,10 @@
         <v>17</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>24</v>
@@ -6187,7 +6190,7 @@
         <v>17</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>21</v>
@@ -6198,7 +6201,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -6210,10 +6213,10 @@
         <v>17</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>24</v>
@@ -6231,7 +6234,7 @@
         <v>17</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>21</v>
@@ -6242,7 +6245,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -6254,10 +6257,10 @@
         <v>17</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>24</v>
@@ -6286,7 +6289,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6298,10 +6301,10 @@
         <v>17</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>24</v>
@@ -6330,7 +6333,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6342,10 +6345,10 @@
         <v>17</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>24</v>
@@ -6374,7 +6377,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -6386,10 +6389,10 @@
         <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>24</v>
@@ -6418,25 +6421,25 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>17</v>
@@ -6451,7 +6454,7 @@
         <v>17</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>27</v>
@@ -6462,7 +6465,7 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
@@ -6474,10 +6477,10 @@
         <v>17</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>24</v>
@@ -6506,7 +6509,7 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>15</v>
@@ -6518,10 +6521,10 @@
         <v>17</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>24</v>
@@ -6542,7 +6545,7 @@
         <v>20</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>17</v>
@@ -6550,7 +6553,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>15</v>
@@ -6562,10 +6565,10 @@
         <v>17</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>24</v>
@@ -6583,7 +6586,7 @@
         <v>17</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>21</v>
@@ -6594,7 +6597,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>15</v>
@@ -6606,10 +6609,10 @@
         <v>17</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>24</v>
@@ -6638,7 +6641,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>15</v>
@@ -6650,10 +6653,10 @@
         <v>17</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>24</v>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>15</v>
@@ -6694,10 +6697,10 @@
         <v>17</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>24</v>
@@ -6726,7 +6729,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>15</v>
@@ -6738,10 +6741,10 @@
         <v>17</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>24</v>
@@ -6759,10 +6762,10 @@
         <v>17</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>17</v>
@@ -6770,7 +6773,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>15</v>
@@ -6782,10 +6785,10 @@
         <v>17</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>24</v>
@@ -6803,7 +6806,7 @@
         <v>17</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>21</v>
@@ -6826,10 +6829,10 @@
         <v>17</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>19</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -6870,10 +6873,10 @@
         <v>17</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>24</v>
@@ -6891,7 +6894,7 @@
         <v>17</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>21</v>
@@ -6902,7 +6905,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>15</v>
@@ -6914,10 +6917,10 @@
         <v>17</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>24</v>
@@ -6946,7 +6949,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>15</v>
@@ -6958,25 +6961,25 @@
         <v>37</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>20</v>
@@ -6985,12 +6988,12 @@
         <v>21</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>15</v>
@@ -7002,10 +7005,10 @@
         <v>17</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>24</v>
@@ -7023,7 +7026,7 @@
         <v>17</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M124" s="2" t="s">
         <v>27</v>
@@ -7034,7 +7037,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>15</v>
@@ -7046,10 +7049,10 @@
         <v>17</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>24</v>
@@ -7078,7 +7081,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>15</v>
@@ -7090,10 +7093,10 @@
         <v>17</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>24</v>
@@ -7111,7 +7114,7 @@
         <v>17</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M126" s="2" t="s">
         <v>21</v>
@@ -7134,10 +7137,10 @@
         <v>17</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>19</v>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>15</v>
@@ -7178,39 +7181,39 @@
         <v>37</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>15</v>
@@ -7222,10 +7225,10 @@
         <v>17</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>24</v>
@@ -7243,7 +7246,7 @@
         <v>17</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M129" s="2" t="s">
         <v>21</v>
@@ -7254,7 +7257,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>15</v>
@@ -7266,39 +7269,39 @@
         <v>37</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>15</v>
@@ -7310,10 +7313,10 @@
         <v>17</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>24</v>
@@ -7342,7 +7345,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>15</v>
@@ -7354,10 +7357,10 @@
         <v>17</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>24</v>
@@ -7386,7 +7389,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>15</v>
@@ -7398,10 +7401,10 @@
         <v>17</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>24</v>
@@ -7430,7 +7433,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>15</v>
@@ -7442,39 +7445,39 @@
         <v>37</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L134" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>15</v>
@@ -7486,10 +7489,10 @@
         <v>17</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>24</v>
@@ -7518,7 +7521,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>15</v>
@@ -7530,10 +7533,10 @@
         <v>17</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>24</v>
@@ -7562,7 +7565,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>15</v>
@@ -7574,10 +7577,10 @@
         <v>37</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>19</v>
@@ -7586,27 +7589,27 @@
         <v>40</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M137" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>15</v>
@@ -7618,10 +7621,10 @@
         <v>17</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>24</v>
@@ -7639,7 +7642,7 @@
         <v>17</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M138" s="2" t="s">
         <v>27</v>
@@ -7650,7 +7653,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>15</v>
@@ -7662,10 +7665,10 @@
         <v>17</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>24</v>
@@ -7694,7 +7697,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>15</v>
@@ -7706,10 +7709,10 @@
         <v>17</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>24</v>
@@ -7738,7 +7741,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>15</v>
@@ -7750,10 +7753,10 @@
         <v>17</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>24</v>
@@ -7771,7 +7774,7 @@
         <v>17</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M141" s="2" t="s">
         <v>27</v>
@@ -7794,10 +7797,10 @@
         <v>17</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>19</v>
@@ -7815,7 +7818,7 @@
         <v>17</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M142" s="2" t="s">
         <v>21</v>
@@ -7826,7 +7829,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>15</v>
@@ -7838,10 +7841,10 @@
         <v>17</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>24</v>
@@ -7870,7 +7873,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>15</v>
@@ -7882,10 +7885,10 @@
         <v>17</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>24</v>
@@ -7914,22 +7917,22 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>24</v>
@@ -7947,10 +7950,10 @@
         <v>17</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N145" s="2" t="s">
         <v>17</v>
@@ -7958,7 +7961,7 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>15</v>
@@ -7970,10 +7973,10 @@
         <v>17</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>24</v>
@@ -7994,7 +7997,7 @@
         <v>20</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N146" s="2" t="s">
         <v>17</v>
@@ -8002,7 +8005,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>15</v>
@@ -8014,10 +8017,10 @@
         <v>17</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>24</v>
@@ -8046,7 +8049,7 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>15</v>
@@ -8058,10 +8061,10 @@
         <v>17</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>24</v>
@@ -8090,7 +8093,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>15</v>
@@ -8102,39 +8105,39 @@
         <v>37</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M149" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>15</v>
@@ -8146,10 +8149,10 @@
         <v>17</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>24</v>
@@ -8190,10 +8193,10 @@
         <v>17</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>19</v>
@@ -8222,7 +8225,7 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>15</v>
@@ -8234,39 +8237,39 @@
         <v>37</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K152" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>15</v>
@@ -8278,10 +8281,10 @@
         <v>17</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>19</v>
@@ -8299,10 +8302,10 @@
         <v>17</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>17</v>
@@ -8310,7 +8313,7 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>15</v>
@@ -8322,10 +8325,10 @@
         <v>17</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>24</v>
@@ -8343,10 +8346,10 @@
         <v>17</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>17</v>
@@ -8354,7 +8357,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>15</v>
@@ -8366,10 +8369,10 @@
         <v>17</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>24</v>
@@ -8398,7 +8401,7 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>15</v>
@@ -8410,10 +8413,10 @@
         <v>17</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>24</v>
@@ -8431,7 +8434,7 @@
         <v>17</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M156" s="2" t="s">
         <v>21</v>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>15</v>
@@ -8454,10 +8457,10 @@
         <v>17</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>24</v>
@@ -8497,23 +8500,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -8521,16 +8524,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -8549,7 +8552,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -8562,7 +8565,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -8570,7 +8573,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -8601,12 +8604,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B2">
         <v>156</v>
@@ -8630,25 +8633,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -8665,13 +8668,13 @@
         <v>127</v>
       </c>
       <c r="G10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -8703,13 +8706,13 @@
         <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K11">
         <v>156</v>
       </c>
       <c r="M11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N11">
         <v>43</v>
@@ -8718,12 +8721,12 @@
         <v>21</v>
       </c>
       <c r="Q11">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -8735,79 +8738,79 @@
         <v>114</v>
       </c>
       <c r="M12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="P13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q13">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -8815,7 +8818,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -8823,7 +8826,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -8831,7 +8834,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -8842,7 +8845,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -8850,16 +8853,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8870,7 +8873,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>38</v>
@@ -8887,105 +8890,105 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
